--- a/artfynd/A 43905-2025 artfynd.xlsx
+++ b/artfynd/A 43905-2025 artfynd.xlsx
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129910394</v>
+        <v>129910400</v>
       </c>
       <c r="B2" t="n">
-        <v>98785</v>
+        <v>92317</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>3298</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>453038</v>
+        <v>453037</v>
       </c>
       <c r="R2" t="n">
-        <v>6911817</v>
+        <v>6911837</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -758,36 +758,46 @@
         <v>0</v>
       </c>
       <c r="AT2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>Fredrika Becker</t>
+        </is>
+      </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>Fredrika Becker</t>
+        </is>
+      </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129910389</v>
+        <v>129910382</v>
       </c>
       <c r="B3" t="n">
-        <v>98785</v>
+        <v>80222</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>6464</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -797,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>453044</v>
+        <v>453112</v>
       </c>
       <c r="R3" t="n">
-        <v>6911918</v>
+        <v>6911956</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -845,36 +855,46 @@
         <v>0</v>
       </c>
       <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Fredrika Becker</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Fredrika Becker</t>
+        </is>
+      </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129910400</v>
+        <v>129910389</v>
       </c>
       <c r="B4" t="n">
-        <v>92317</v>
+        <v>98790</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>3298</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -884,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>453037</v>
+        <v>453044</v>
       </c>
       <c r="R4" t="n">
-        <v>6911837</v>
+        <v>6911918</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -932,36 +952,46 @@
         <v>0</v>
       </c>
       <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Fredrika Becker</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Fredrika Becker</t>
+        </is>
+      </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129910382</v>
+        <v>129910394</v>
       </c>
       <c r="B5" t="n">
-        <v>80222</v>
+        <v>98790</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6464</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -971,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>453112</v>
+        <v>453038</v>
       </c>
       <c r="R5" t="n">
-        <v>6911956</v>
+        <v>6911817</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1019,14 +1049,24 @@
         <v>0</v>
       </c>
       <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Fredrika Becker</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Fredrika Becker</t>
+        </is>
+      </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129910396</v>
+        <v>129910383</v>
       </c>
       <c r="B6" t="n">
-        <v>92317</v>
+        <v>80222</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1034,21 +1074,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>3298</v>
+        <v>6464</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1058,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>453014</v>
+        <v>453095</v>
       </c>
       <c r="R6" t="n">
-        <v>6911798</v>
+        <v>6911956</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1106,14 +1146,24 @@
         <v>0</v>
       </c>
       <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Fredrika Becker</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Fredrika Becker</t>
+        </is>
+      </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129910383</v>
+        <v>129910396</v>
       </c>
       <c r="B7" t="n">
-        <v>80222</v>
+        <v>92317</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1121,21 +1171,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6464</v>
+        <v>3298</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1145,10 +1195,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>453095</v>
+        <v>453014</v>
       </c>
       <c r="R7" t="n">
-        <v>6911956</v>
+        <v>6911798</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1193,6 +1243,16 @@
         <v>0</v>
       </c>
       <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Fredrika Becker</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Fredrika Becker</t>
+        </is>
+      </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
@@ -1280,6 +1340,16 @@
         <v>0</v>
       </c>
       <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Fredrika Becker</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Fredrika Becker</t>
+        </is>
+      </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
@@ -1367,6 +1437,16 @@
         <v>0</v>
       </c>
       <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Fredrika Becker</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Fredrika Becker</t>
+        </is>
+      </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
@@ -1450,36 +1530,46 @@
         <v>0</v>
       </c>
       <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Fredrika Becker</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Fredrika Becker</t>
+        </is>
+      </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129910393</v>
+        <v>129910397</v>
       </c>
       <c r="B11" t="n">
-        <v>91599</v>
+        <v>91563</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1489,10 +1579,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>453075</v>
+        <v>452975</v>
       </c>
       <c r="R11" t="n">
-        <v>6911909</v>
+        <v>6911774</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1537,6 +1627,16 @@
         <v>0</v>
       </c>
       <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Fredrika Becker</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Fredrika Becker</t>
+        </is>
+      </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
@@ -1544,7 +1644,7 @@
         <v>129910391</v>
       </c>
       <c r="B12" t="n">
-        <v>96011</v>
+        <v>96016</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1624,36 +1724,46 @@
         <v>0</v>
       </c>
       <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Fredrika Becker</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Fredrika Becker</t>
+        </is>
+      </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129910397</v>
+        <v>129910393</v>
       </c>
       <c r="B13" t="n">
-        <v>91563</v>
+        <v>91599</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1663,10 +1773,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>452975</v>
+        <v>453075</v>
       </c>
       <c r="R13" t="n">
-        <v>6911774</v>
+        <v>6911909</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -1711,6 +1821,16 @@
         <v>0</v>
       </c>
       <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Fredrika Becker</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Fredrika Becker</t>
+        </is>
+      </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
@@ -1798,6 +1918,16 @@
         <v>0</v>
       </c>
       <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Fredrika Becker</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Fredrika Becker</t>
+        </is>
+      </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
@@ -1885,6 +2015,16 @@
         <v>0</v>
       </c>
       <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Fredrika Becker</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Fredrika Becker</t>
+        </is>
+      </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
@@ -1972,6 +2112,16 @@
         <v>0</v>
       </c>
       <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Fredrika Becker</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Fredrika Becker</t>
+        </is>
+      </c>
       <c r="AY16" t="inlineStr"/>
     </row>
   </sheetData>

--- a/artfynd/A 43905-2025 artfynd.xlsx
+++ b/artfynd/A 43905-2025 artfynd.xlsx
@@ -1544,32 +1544,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129910397</v>
+        <v>129910393</v>
       </c>
       <c r="B11" t="n">
-        <v>91563</v>
+        <v>91599</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1579,10 +1579,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>452975</v>
+        <v>453075</v>
       </c>
       <c r="R11" t="n">
-        <v>6911774</v>
+        <v>6911909</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1641,10 +1641,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129910391</v>
+        <v>129910397</v>
       </c>
       <c r="B12" t="n">
-        <v>96016</v>
+        <v>91563</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1652,21 +1652,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>2809</v>
+        <v>5447</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1676,10 +1676,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>453075</v>
+        <v>452975</v>
       </c>
       <c r="R12" t="n">
-        <v>6911909</v>
+        <v>6911774</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1738,32 +1738,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129910393</v>
+        <v>129910391</v>
       </c>
       <c r="B13" t="n">
-        <v>91599</v>
+        <v>96016</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1202</v>
+        <v>2809</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>

--- a/artfynd/A 43905-2025 artfynd.xlsx
+++ b/artfynd/A 43905-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129910400</v>
+        <v>129910382</v>
       </c>
       <c r="B2" t="n">
-        <v>92317</v>
+        <v>80225</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>3298</v>
+        <v>6464</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>453037</v>
+        <v>453112</v>
       </c>
       <c r="R2" t="n">
-        <v>6911837</v>
+        <v>6911956</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -772,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129910382</v>
+        <v>129910400</v>
       </c>
       <c r="B3" t="n">
-        <v>80222</v>
+        <v>92320</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -783,21 +783,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6464</v>
+        <v>3298</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>453112</v>
+        <v>453037</v>
       </c>
       <c r="R3" t="n">
-        <v>6911956</v>
+        <v>6911837</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -872,7 +872,7 @@
         <v>129910389</v>
       </c>
       <c r="B4" t="n">
-        <v>98790</v>
+        <v>98794</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>129910394</v>
       </c>
       <c r="B5" t="n">
-        <v>98790</v>
+        <v>98794</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1063,10 +1063,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129910383</v>
+        <v>129910396</v>
       </c>
       <c r="B6" t="n">
-        <v>80222</v>
+        <v>92320</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1074,21 +1074,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6464</v>
+        <v>3298</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1098,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>453095</v>
+        <v>453014</v>
       </c>
       <c r="R6" t="n">
-        <v>6911956</v>
+        <v>6911798</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1160,10 +1160,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129910396</v>
+        <v>129910383</v>
       </c>
       <c r="B7" t="n">
-        <v>92317</v>
+        <v>80225</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1171,21 +1171,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>3298</v>
+        <v>6464</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1195,10 +1195,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>453014</v>
+        <v>453095</v>
       </c>
       <c r="R7" t="n">
-        <v>6911798</v>
+        <v>6911956</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1260,7 +1260,7 @@
         <v>129910381</v>
       </c>
       <c r="B8" t="n">
-        <v>80186</v>
+        <v>80189</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1357,7 +1357,7 @@
         <v>129910380</v>
       </c>
       <c r="B9" t="n">
-        <v>79081</v>
+        <v>79084</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1454,7 +1454,7 @@
         <v>129910392</v>
       </c>
       <c r="B10" t="n">
-        <v>91619</v>
+        <v>91622</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1547,7 +1547,7 @@
         <v>129910393</v>
       </c>
       <c r="B11" t="n">
-        <v>91599</v>
+        <v>91602</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1641,10 +1641,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129910397</v>
+        <v>129910391</v>
       </c>
       <c r="B12" t="n">
-        <v>91563</v>
+        <v>96020</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1652,21 +1652,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5447</v>
+        <v>2809</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1676,10 +1676,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>452975</v>
+        <v>453075</v>
       </c>
       <c r="R12" t="n">
-        <v>6911774</v>
+        <v>6911909</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1738,10 +1738,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129910391</v>
+        <v>129910397</v>
       </c>
       <c r="B13" t="n">
-        <v>96016</v>
+        <v>91566</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1749,21 +1749,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>2809</v>
+        <v>5447</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1773,10 +1773,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>453075</v>
+        <v>452975</v>
       </c>
       <c r="R13" t="n">
-        <v>6911909</v>
+        <v>6911774</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -1838,7 +1838,7 @@
         <v>129910388</v>
       </c>
       <c r="B14" t="n">
-        <v>79081</v>
+        <v>79084</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1935,7 +1935,7 @@
         <v>129910390</v>
       </c>
       <c r="B15" t="n">
-        <v>91563</v>
+        <v>91566</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2032,7 +2032,7 @@
         <v>129910398</v>
       </c>
       <c r="B16" t="n">
-        <v>91599</v>
+        <v>91602</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>

--- a/artfynd/A 43905-2025 artfynd.xlsx
+++ b/artfynd/A 43905-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129910382</v>
+        <v>129910400</v>
       </c>
       <c r="B2" t="n">
-        <v>80225</v>
+        <v>92320</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6464</v>
+        <v>3298</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>453112</v>
+        <v>453037</v>
       </c>
       <c r="R2" t="n">
-        <v>6911956</v>
+        <v>6911837</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -772,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129910400</v>
+        <v>129910382</v>
       </c>
       <c r="B3" t="n">
-        <v>92320</v>
+        <v>80225</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -783,21 +783,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>3298</v>
+        <v>6464</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>453037</v>
+        <v>453112</v>
       </c>
       <c r="R3" t="n">
-        <v>6911837</v>
+        <v>6911956</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>

--- a/artfynd/A 43905-2025 artfynd.xlsx
+++ b/artfynd/A 43905-2025 artfynd.xlsx
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129910400</v>
+        <v>129910389</v>
       </c>
       <c r="B2" t="n">
-        <v>92320</v>
+        <v>98794</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>3298</v>
+        <v>220787</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>453037</v>
+        <v>453044</v>
       </c>
       <c r="R2" t="n">
-        <v>6911837</v>
+        <v>6911918</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -772,32 +772,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129910382</v>
+        <v>129910394</v>
       </c>
       <c r="B3" t="n">
-        <v>80225</v>
+        <v>98794</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6464</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>453112</v>
+        <v>453038</v>
       </c>
       <c r="R3" t="n">
-        <v>6911956</v>
+        <v>6911817</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -869,32 +869,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129910389</v>
+        <v>129910382</v>
       </c>
       <c r="B4" t="n">
-        <v>98794</v>
+        <v>80225</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>6464</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -904,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>453044</v>
+        <v>453112</v>
       </c>
       <c r="R4" t="n">
-        <v>6911918</v>
+        <v>6911956</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -966,32 +966,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129910394</v>
+        <v>129910400</v>
       </c>
       <c r="B5" t="n">
-        <v>98794</v>
+        <v>92320</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>3298</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1001,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>453038</v>
+        <v>453037</v>
       </c>
       <c r="R5" t="n">
-        <v>6911817</v>
+        <v>6911837</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1544,32 +1544,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129910393</v>
+        <v>129910391</v>
       </c>
       <c r="B11" t="n">
-        <v>91602</v>
+        <v>96020</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1202</v>
+        <v>2809</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1641,10 +1641,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129910391</v>
+        <v>129910397</v>
       </c>
       <c r="B12" t="n">
-        <v>96020</v>
+        <v>91566</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1652,21 +1652,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>2809</v>
+        <v>5447</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1676,10 +1676,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>453075</v>
+        <v>452975</v>
       </c>
       <c r="R12" t="n">
-        <v>6911909</v>
+        <v>6911774</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1738,32 +1738,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129910397</v>
+        <v>129910393</v>
       </c>
       <c r="B13" t="n">
-        <v>91566</v>
+        <v>91602</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1773,10 +1773,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>452975</v>
+        <v>453075</v>
       </c>
       <c r="R13" t="n">
-        <v>6911774</v>
+        <v>6911909</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>

--- a/artfynd/A 43905-2025 artfynd.xlsx
+++ b/artfynd/A 43905-2025 artfynd.xlsx
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129910389</v>
+        <v>129910400</v>
       </c>
       <c r="B2" t="n">
-        <v>98794</v>
+        <v>92323</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>3298</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>453044</v>
+        <v>453037</v>
       </c>
       <c r="R2" t="n">
-        <v>6911918</v>
+        <v>6911837</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -772,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129910394</v>
+        <v>129910389</v>
       </c>
       <c r="B3" t="n">
-        <v>98794</v>
+        <v>98797</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>453038</v>
+        <v>453044</v>
       </c>
       <c r="R3" t="n">
-        <v>6911817</v>
+        <v>6911918</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -869,32 +869,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129910382</v>
+        <v>129910394</v>
       </c>
       <c r="B4" t="n">
-        <v>80225</v>
+        <v>98797</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6464</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -904,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>453112</v>
+        <v>453038</v>
       </c>
       <c r="R4" t="n">
-        <v>6911956</v>
+        <v>6911817</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -966,10 +966,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129910400</v>
+        <v>129910382</v>
       </c>
       <c r="B5" t="n">
-        <v>92320</v>
+        <v>80228</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -977,21 +977,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>3298</v>
+        <v>6464</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1001,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>453037</v>
+        <v>453112</v>
       </c>
       <c r="R5" t="n">
-        <v>6911837</v>
+        <v>6911956</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1063,10 +1063,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129910396</v>
+        <v>129910383</v>
       </c>
       <c r="B6" t="n">
-        <v>92320</v>
+        <v>80228</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1074,21 +1074,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>3298</v>
+        <v>6464</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1098,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>453014</v>
+        <v>453095</v>
       </c>
       <c r="R6" t="n">
-        <v>6911798</v>
+        <v>6911956</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1160,10 +1160,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129910383</v>
+        <v>129910396</v>
       </c>
       <c r="B7" t="n">
-        <v>80225</v>
+        <v>92323</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1171,21 +1171,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6464</v>
+        <v>3298</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1195,10 +1195,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>453095</v>
+        <v>453014</v>
       </c>
       <c r="R7" t="n">
-        <v>6911956</v>
+        <v>6911798</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1260,7 +1260,7 @@
         <v>129910381</v>
       </c>
       <c r="B8" t="n">
-        <v>80189</v>
+        <v>80192</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1357,7 +1357,7 @@
         <v>129910380</v>
       </c>
       <c r="B9" t="n">
-        <v>79084</v>
+        <v>79087</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1454,7 +1454,7 @@
         <v>129910392</v>
       </c>
       <c r="B10" t="n">
-        <v>91622</v>
+        <v>91625</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1547,7 +1547,7 @@
         <v>129910391</v>
       </c>
       <c r="B11" t="n">
-        <v>96020</v>
+        <v>96023</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1641,32 +1641,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129910397</v>
+        <v>129910393</v>
       </c>
       <c r="B12" t="n">
-        <v>91566</v>
+        <v>91605</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1676,10 +1676,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>452975</v>
+        <v>453075</v>
       </c>
       <c r="R12" t="n">
-        <v>6911774</v>
+        <v>6911909</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1738,32 +1738,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129910393</v>
+        <v>129910397</v>
       </c>
       <c r="B13" t="n">
-        <v>91602</v>
+        <v>91569</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1773,10 +1773,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>453075</v>
+        <v>452975</v>
       </c>
       <c r="R13" t="n">
-        <v>6911909</v>
+        <v>6911774</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -1838,7 +1838,7 @@
         <v>129910388</v>
       </c>
       <c r="B14" t="n">
-        <v>79084</v>
+        <v>79087</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1935,7 +1935,7 @@
         <v>129910390</v>
       </c>
       <c r="B15" t="n">
-        <v>91566</v>
+        <v>91569</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2032,7 +2032,7 @@
         <v>129910398</v>
       </c>
       <c r="B16" t="n">
-        <v>91602</v>
+        <v>91605</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>

--- a/artfynd/A 43905-2025 artfynd.xlsx
+++ b/artfynd/A 43905-2025 artfynd.xlsx
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129910400</v>
+        <v>129910389</v>
       </c>
       <c r="B2" t="n">
-        <v>92323</v>
+        <v>98797</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>3298</v>
+        <v>220787</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>453037</v>
+        <v>453044</v>
       </c>
       <c r="R2" t="n">
-        <v>6911837</v>
+        <v>6911918</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -772,7 +772,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129910389</v>
+        <v>129910394</v>
       </c>
       <c r="B3" t="n">
         <v>98797</v>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>453044</v>
+        <v>453038</v>
       </c>
       <c r="R3" t="n">
-        <v>6911918</v>
+        <v>6911817</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -869,32 +869,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129910394</v>
+        <v>129910400</v>
       </c>
       <c r="B4" t="n">
-        <v>98797</v>
+        <v>92323</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>3298</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -904,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>453038</v>
+        <v>453037</v>
       </c>
       <c r="R4" t="n">
-        <v>6911817</v>
+        <v>6911837</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -1544,32 +1544,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129910391</v>
+        <v>129910393</v>
       </c>
       <c r="B11" t="n">
-        <v>96023</v>
+        <v>91605</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>2809</v>
+        <v>1202</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1641,32 +1641,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129910393</v>
+        <v>129910397</v>
       </c>
       <c r="B12" t="n">
-        <v>91605</v>
+        <v>91569</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1676,10 +1676,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>453075</v>
+        <v>452975</v>
       </c>
       <c r="R12" t="n">
-        <v>6911909</v>
+        <v>6911774</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1738,10 +1738,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129910397</v>
+        <v>129910391</v>
       </c>
       <c r="B13" t="n">
-        <v>91569</v>
+        <v>96023</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1749,21 +1749,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>5447</v>
+        <v>2809</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1773,10 +1773,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>452975</v>
+        <v>453075</v>
       </c>
       <c r="R13" t="n">
-        <v>6911774</v>
+        <v>6911909</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>

--- a/artfynd/A 43905-2025 artfynd.xlsx
+++ b/artfynd/A 43905-2025 artfynd.xlsx
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129910389</v>
+        <v>129910382</v>
       </c>
       <c r="B2" t="n">
-        <v>98797</v>
+        <v>80229</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>6464</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>453044</v>
+        <v>453112</v>
       </c>
       <c r="R2" t="n">
-        <v>6911918</v>
+        <v>6911956</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -772,32 +772,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129910394</v>
+        <v>129910400</v>
       </c>
       <c r="B3" t="n">
-        <v>98797</v>
+        <v>92324</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>3298</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>453038</v>
+        <v>453037</v>
       </c>
       <c r="R3" t="n">
-        <v>6911817</v>
+        <v>6911837</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -869,32 +869,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129910400</v>
+        <v>129910389</v>
       </c>
       <c r="B4" t="n">
-        <v>92323</v>
+        <v>98798</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>3298</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -904,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>453037</v>
+        <v>453044</v>
       </c>
       <c r="R4" t="n">
-        <v>6911837</v>
+        <v>6911918</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -966,32 +966,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129910382</v>
+        <v>129910394</v>
       </c>
       <c r="B5" t="n">
-        <v>80228</v>
+        <v>98798</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6464</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1001,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>453112</v>
+        <v>453038</v>
       </c>
       <c r="R5" t="n">
-        <v>6911956</v>
+        <v>6911817</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1066,7 +1066,7 @@
         <v>129910383</v>
       </c>
       <c r="B6" t="n">
-        <v>80228</v>
+        <v>80229</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1163,7 +1163,7 @@
         <v>129910396</v>
       </c>
       <c r="B7" t="n">
-        <v>92323</v>
+        <v>92324</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
         <v>129910381</v>
       </c>
       <c r="B8" t="n">
-        <v>80192</v>
+        <v>80193</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1357,7 +1357,7 @@
         <v>129910380</v>
       </c>
       <c r="B9" t="n">
-        <v>79087</v>
+        <v>79088</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1454,7 +1454,7 @@
         <v>129910392</v>
       </c>
       <c r="B10" t="n">
-        <v>91625</v>
+        <v>91626</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1547,7 +1547,7 @@
         <v>129910393</v>
       </c>
       <c r="B11" t="n">
-        <v>91605</v>
+        <v>91606</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1644,7 +1644,7 @@
         <v>129910397</v>
       </c>
       <c r="B12" t="n">
-        <v>91569</v>
+        <v>91570</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1741,7 +1741,7 @@
         <v>129910391</v>
       </c>
       <c r="B13" t="n">
-        <v>96023</v>
+        <v>96024</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1838,7 +1838,7 @@
         <v>129910388</v>
       </c>
       <c r="B14" t="n">
-        <v>79087</v>
+        <v>79088</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1935,7 +1935,7 @@
         <v>129910390</v>
       </c>
       <c r="B15" t="n">
-        <v>91569</v>
+        <v>91570</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2032,7 +2032,7 @@
         <v>129910398</v>
       </c>
       <c r="B16" t="n">
-        <v>91605</v>
+        <v>91606</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>

--- a/artfynd/A 43905-2025 artfynd.xlsx
+++ b/artfynd/A 43905-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129910382</v>
+        <v>129910400</v>
       </c>
       <c r="B2" t="n">
-        <v>80229</v>
+        <v>92324</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6464</v>
+        <v>3298</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>453112</v>
+        <v>453037</v>
       </c>
       <c r="R2" t="n">
-        <v>6911956</v>
+        <v>6911837</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -772,32 +772,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129910400</v>
+        <v>129910389</v>
       </c>
       <c r="B3" t="n">
-        <v>92324</v>
+        <v>98798</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>3298</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>453037</v>
+        <v>453044</v>
       </c>
       <c r="R3" t="n">
-        <v>6911837</v>
+        <v>6911918</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -869,7 +869,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129910389</v>
+        <v>129910394</v>
       </c>
       <c r="B4" t="n">
         <v>98798</v>
@@ -904,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>453044</v>
+        <v>453038</v>
       </c>
       <c r="R4" t="n">
-        <v>6911918</v>
+        <v>6911817</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -966,32 +966,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129910394</v>
+        <v>129910382</v>
       </c>
       <c r="B5" t="n">
-        <v>98798</v>
+        <v>80229</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>6464</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1001,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>453038</v>
+        <v>453112</v>
       </c>
       <c r="R5" t="n">
-        <v>6911817</v>
+        <v>6911956</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1641,10 +1641,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129910397</v>
+        <v>129910391</v>
       </c>
       <c r="B12" t="n">
-        <v>91570</v>
+        <v>96024</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1652,21 +1652,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5447</v>
+        <v>2809</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1676,10 +1676,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>452975</v>
+        <v>453075</v>
       </c>
       <c r="R12" t="n">
-        <v>6911774</v>
+        <v>6911909</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1738,10 +1738,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129910391</v>
+        <v>129910397</v>
       </c>
       <c r="B13" t="n">
-        <v>96024</v>
+        <v>91570</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1749,21 +1749,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>2809</v>
+        <v>5447</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1773,10 +1773,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>453075</v>
+        <v>452975</v>
       </c>
       <c r="R13" t="n">
-        <v>6911909</v>
+        <v>6911774</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>

--- a/artfynd/A 43905-2025 artfynd.xlsx
+++ b/artfynd/A 43905-2025 artfynd.xlsx
@@ -1063,10 +1063,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129910383</v>
+        <v>129910396</v>
       </c>
       <c r="B6" t="n">
-        <v>80229</v>
+        <v>92324</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1074,21 +1074,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6464</v>
+        <v>3298</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1098,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>453095</v>
+        <v>453014</v>
       </c>
       <c r="R6" t="n">
-        <v>6911956</v>
+        <v>6911798</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1160,10 +1160,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129910396</v>
+        <v>129910383</v>
       </c>
       <c r="B7" t="n">
-        <v>92324</v>
+        <v>80229</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1171,21 +1171,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>3298</v>
+        <v>6464</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1195,10 +1195,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>453014</v>
+        <v>453095</v>
       </c>
       <c r="R7" t="n">
-        <v>6911798</v>
+        <v>6911956</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1641,10 +1641,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129910391</v>
+        <v>129910397</v>
       </c>
       <c r="B12" t="n">
-        <v>96024</v>
+        <v>91570</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1652,21 +1652,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>2809</v>
+        <v>5447</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1676,10 +1676,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>453075</v>
+        <v>452975</v>
       </c>
       <c r="R12" t="n">
-        <v>6911909</v>
+        <v>6911774</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1738,10 +1738,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129910397</v>
+        <v>129910391</v>
       </c>
       <c r="B13" t="n">
-        <v>91570</v>
+        <v>96024</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1749,21 +1749,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>5447</v>
+        <v>2809</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1773,10 +1773,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>452975</v>
+        <v>453075</v>
       </c>
       <c r="R13" t="n">
-        <v>6911774</v>
+        <v>6911909</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>

--- a/artfynd/A 43905-2025 artfynd.xlsx
+++ b/artfynd/A 43905-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129910400</v>
+        <v>129910382</v>
       </c>
       <c r="B2" t="n">
-        <v>92324</v>
+        <v>80230</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>3298</v>
+        <v>6464</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>453037</v>
+        <v>453112</v>
       </c>
       <c r="R2" t="n">
-        <v>6911837</v>
+        <v>6911956</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -772,32 +772,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129910389</v>
+        <v>129910400</v>
       </c>
       <c r="B3" t="n">
-        <v>98798</v>
+        <v>92341</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>3298</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>453044</v>
+        <v>453037</v>
       </c>
       <c r="R3" t="n">
-        <v>6911918</v>
+        <v>6911837</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -869,10 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129910394</v>
+        <v>129910389</v>
       </c>
       <c r="B4" t="n">
-        <v>98798</v>
+        <v>98815</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -904,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>453038</v>
+        <v>453044</v>
       </c>
       <c r="R4" t="n">
-        <v>6911817</v>
+        <v>6911918</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -966,32 +966,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129910382</v>
+        <v>129910394</v>
       </c>
       <c r="B5" t="n">
-        <v>80229</v>
+        <v>98815</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6464</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1001,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>453112</v>
+        <v>453038</v>
       </c>
       <c r="R5" t="n">
-        <v>6911956</v>
+        <v>6911817</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1063,10 +1063,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129910396</v>
+        <v>129910383</v>
       </c>
       <c r="B6" t="n">
-        <v>92324</v>
+        <v>80230</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1074,21 +1074,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>3298</v>
+        <v>6464</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1098,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>453014</v>
+        <v>453095</v>
       </c>
       <c r="R6" t="n">
-        <v>6911798</v>
+        <v>6911956</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1160,10 +1160,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129910383</v>
+        <v>129910396</v>
       </c>
       <c r="B7" t="n">
-        <v>80229</v>
+        <v>92341</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1171,21 +1171,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6464</v>
+        <v>3298</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1195,10 +1195,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>453095</v>
+        <v>453014</v>
       </c>
       <c r="R7" t="n">
-        <v>6911956</v>
+        <v>6911798</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1260,7 +1260,7 @@
         <v>129910381</v>
       </c>
       <c r="B8" t="n">
-        <v>80193</v>
+        <v>80194</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1357,7 +1357,7 @@
         <v>129910380</v>
       </c>
       <c r="B9" t="n">
-        <v>79088</v>
+        <v>79089</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1454,7 +1454,7 @@
         <v>129910392</v>
       </c>
       <c r="B10" t="n">
-        <v>91626</v>
+        <v>91643</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1544,32 +1544,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129910393</v>
+        <v>129910391</v>
       </c>
       <c r="B11" t="n">
-        <v>91606</v>
+        <v>96041</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1202</v>
+        <v>2809</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1641,32 +1641,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129910397</v>
+        <v>129910393</v>
       </c>
       <c r="B12" t="n">
-        <v>91570</v>
+        <v>91623</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1676,10 +1676,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>452975</v>
+        <v>453075</v>
       </c>
       <c r="R12" t="n">
-        <v>6911774</v>
+        <v>6911909</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1738,10 +1738,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129910391</v>
+        <v>129910397</v>
       </c>
       <c r="B13" t="n">
-        <v>96024</v>
+        <v>91587</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1749,21 +1749,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>2809</v>
+        <v>5447</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1773,10 +1773,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>453075</v>
+        <v>452975</v>
       </c>
       <c r="R13" t="n">
-        <v>6911909</v>
+        <v>6911774</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -1838,7 +1838,7 @@
         <v>129910388</v>
       </c>
       <c r="B14" t="n">
-        <v>79088</v>
+        <v>79089</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1935,7 +1935,7 @@
         <v>129910390</v>
       </c>
       <c r="B15" t="n">
-        <v>91570</v>
+        <v>91587</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2032,7 +2032,7 @@
         <v>129910398</v>
       </c>
       <c r="B16" t="n">
-        <v>91606</v>
+        <v>91623</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>

--- a/artfynd/A 43905-2025 artfynd.xlsx
+++ b/artfynd/A 43905-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129910400</v>
+        <v>129910382</v>
       </c>
       <c r="B2" t="n">
-        <v>92357</v>
+        <v>80236</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>3298</v>
+        <v>6464</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>453037</v>
+        <v>453112</v>
       </c>
       <c r="R2" t="n">
-        <v>6911837</v>
+        <v>6911956</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -966,10 +966,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129910382</v>
+        <v>129910400</v>
       </c>
       <c r="B5" t="n">
-        <v>80236</v>
+        <v>92357</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -977,21 +977,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6464</v>
+        <v>3298</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1001,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>453112</v>
+        <v>453037</v>
       </c>
       <c r="R5" t="n">
-        <v>6911956</v>
+        <v>6911837</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1544,10 +1544,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129910397</v>
+        <v>129910391</v>
       </c>
       <c r="B11" t="n">
-        <v>91603</v>
+        <v>96057</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1555,21 +1555,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5447</v>
+        <v>2809</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1579,10 +1579,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>452975</v>
+        <v>453075</v>
       </c>
       <c r="R11" t="n">
-        <v>6911774</v>
+        <v>6911909</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1641,32 +1641,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129910391</v>
+        <v>129910393</v>
       </c>
       <c r="B12" t="n">
-        <v>96057</v>
+        <v>91639</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>2809</v>
+        <v>1202</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1738,32 +1738,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129910393</v>
+        <v>129910397</v>
       </c>
       <c r="B13" t="n">
-        <v>91639</v>
+        <v>91603</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1773,10 +1773,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>453075</v>
+        <v>452975</v>
       </c>
       <c r="R13" t="n">
-        <v>6911909</v>
+        <v>6911774</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>

--- a/artfynd/A 43905-2025 artfynd.xlsx
+++ b/artfynd/A 43905-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129910382</v>
+        <v>129910400</v>
       </c>
       <c r="B2" t="n">
-        <v>80236</v>
+        <v>92359</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6464</v>
+        <v>3298</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>453112</v>
+        <v>453037</v>
       </c>
       <c r="R2" t="n">
-        <v>6911956</v>
+        <v>6911837</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -772,32 +772,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129910389</v>
+        <v>129910382</v>
       </c>
       <c r="B3" t="n">
-        <v>98831</v>
+        <v>80236</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>6464</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>453044</v>
+        <v>453112</v>
       </c>
       <c r="R3" t="n">
-        <v>6911918</v>
+        <v>6911956</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -869,10 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129910394</v>
+        <v>129910389</v>
       </c>
       <c r="B4" t="n">
-        <v>98831</v>
+        <v>98833</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -904,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>453038</v>
+        <v>453044</v>
       </c>
       <c r="R4" t="n">
-        <v>6911817</v>
+        <v>6911918</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -966,32 +966,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129910400</v>
+        <v>129910394</v>
       </c>
       <c r="B5" t="n">
-        <v>92357</v>
+        <v>98833</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>3298</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1001,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>453037</v>
+        <v>453038</v>
       </c>
       <c r="R5" t="n">
-        <v>6911837</v>
+        <v>6911817</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1066,7 +1066,7 @@
         <v>129910396</v>
       </c>
       <c r="B6" t="n">
-        <v>92357</v>
+        <v>92359</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1454,7 +1454,7 @@
         <v>129910392</v>
       </c>
       <c r="B10" t="n">
-        <v>91659</v>
+        <v>91661</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1547,7 +1547,7 @@
         <v>129910391</v>
       </c>
       <c r="B11" t="n">
-        <v>96057</v>
+        <v>96059</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1644,7 +1644,7 @@
         <v>129910393</v>
       </c>
       <c r="B12" t="n">
-        <v>91639</v>
+        <v>91641</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1741,7 +1741,7 @@
         <v>129910397</v>
       </c>
       <c r="B13" t="n">
-        <v>91603</v>
+        <v>91605</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1935,7 +1935,7 @@
         <v>129910390</v>
       </c>
       <c r="B15" t="n">
-        <v>91603</v>
+        <v>91605</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2032,7 +2032,7 @@
         <v>129910398</v>
       </c>
       <c r="B16" t="n">
-        <v>91639</v>
+        <v>91641</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>

--- a/artfynd/A 43905-2025 artfynd.xlsx
+++ b/artfynd/A 43905-2025 artfynd.xlsx
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129910400</v>
+        <v>129910394</v>
       </c>
       <c r="B2" t="n">
-        <v>92359</v>
+        <v>98920</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>3298</v>
+        <v>220787</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>453037</v>
+        <v>453038</v>
       </c>
       <c r="R2" t="n">
-        <v>6911837</v>
+        <v>6911817</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -772,32 +772,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129910382</v>
+        <v>129910389</v>
       </c>
       <c r="B3" t="n">
-        <v>80236</v>
+        <v>98920</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6464</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>453112</v>
+        <v>453044</v>
       </c>
       <c r="R3" t="n">
-        <v>6911956</v>
+        <v>6911918</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -869,32 +869,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129910389</v>
+        <v>129910400</v>
       </c>
       <c r="B4" t="n">
-        <v>98833</v>
+        <v>92446</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>3298</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -904,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>453044</v>
+        <v>453037</v>
       </c>
       <c r="R4" t="n">
-        <v>6911918</v>
+        <v>6911837</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -966,32 +966,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129910394</v>
+        <v>129910382</v>
       </c>
       <c r="B5" t="n">
-        <v>98833</v>
+        <v>80321</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>6464</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1001,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>453038</v>
+        <v>453112</v>
       </c>
       <c r="R5" t="n">
-        <v>6911817</v>
+        <v>6911956</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1063,10 +1063,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129910396</v>
+        <v>129910383</v>
       </c>
       <c r="B6" t="n">
-        <v>92359</v>
+        <v>80321</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1074,21 +1074,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>3298</v>
+        <v>6464</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1098,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>453014</v>
+        <v>453095</v>
       </c>
       <c r="R6" t="n">
-        <v>6911798</v>
+        <v>6911956</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1160,10 +1160,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129910383</v>
+        <v>129910396</v>
       </c>
       <c r="B7" t="n">
-        <v>80236</v>
+        <v>92446</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1171,21 +1171,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6464</v>
+        <v>3298</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1195,10 +1195,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>453095</v>
+        <v>453014</v>
       </c>
       <c r="R7" t="n">
-        <v>6911956</v>
+        <v>6911798</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1260,7 +1260,7 @@
         <v>129910381</v>
       </c>
       <c r="B8" t="n">
-        <v>80200</v>
+        <v>80285</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1357,7 +1357,7 @@
         <v>129910380</v>
       </c>
       <c r="B9" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1454,7 +1454,7 @@
         <v>129910392</v>
       </c>
       <c r="B10" t="n">
-        <v>91661</v>
+        <v>91748</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1547,7 +1547,7 @@
         <v>129910391</v>
       </c>
       <c r="B11" t="n">
-        <v>96059</v>
+        <v>96146</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1644,7 +1644,7 @@
         <v>129910393</v>
       </c>
       <c r="B12" t="n">
-        <v>91641</v>
+        <v>91728</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1741,7 +1741,7 @@
         <v>129910397</v>
       </c>
       <c r="B13" t="n">
-        <v>91605</v>
+        <v>91692</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1838,7 +1838,7 @@
         <v>129910388</v>
       </c>
       <c r="B14" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1935,7 +1935,7 @@
         <v>129910390</v>
       </c>
       <c r="B15" t="n">
-        <v>91605</v>
+        <v>91692</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2032,7 +2032,7 @@
         <v>129910398</v>
       </c>
       <c r="B16" t="n">
-        <v>91641</v>
+        <v>91728</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>

--- a/artfynd/A 43905-2025 artfynd.xlsx
+++ b/artfynd/A 43905-2025 artfynd.xlsx
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129910394</v>
+        <v>129910400</v>
       </c>
       <c r="B2" t="n">
-        <v>98920</v>
+        <v>92359</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>3298</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>453038</v>
+        <v>453037</v>
       </c>
       <c r="R2" t="n">
-        <v>6911817</v>
+        <v>6911837</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -772,32 +772,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129910389</v>
+        <v>129910382</v>
       </c>
       <c r="B3" t="n">
-        <v>98920</v>
+        <v>80236</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>6464</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>453044</v>
+        <v>453112</v>
       </c>
       <c r="R3" t="n">
-        <v>6911918</v>
+        <v>6911956</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -869,32 +869,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129910400</v>
+        <v>129910389</v>
       </c>
       <c r="B4" t="n">
-        <v>92446</v>
+        <v>98833</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>3298</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -904,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>453037</v>
+        <v>453044</v>
       </c>
       <c r="R4" t="n">
-        <v>6911837</v>
+        <v>6911918</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -966,32 +966,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129910382</v>
+        <v>129910394</v>
       </c>
       <c r="B5" t="n">
-        <v>80321</v>
+        <v>98833</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6464</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1001,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>453112</v>
+        <v>453038</v>
       </c>
       <c r="R5" t="n">
-        <v>6911956</v>
+        <v>6911817</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1063,10 +1063,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129910383</v>
+        <v>129910396</v>
       </c>
       <c r="B6" t="n">
-        <v>80321</v>
+        <v>92359</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1074,21 +1074,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6464</v>
+        <v>3298</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1098,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>453095</v>
+        <v>453014</v>
       </c>
       <c r="R6" t="n">
-        <v>6911956</v>
+        <v>6911798</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1160,10 +1160,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129910396</v>
+        <v>129910383</v>
       </c>
       <c r="B7" t="n">
-        <v>92446</v>
+        <v>80236</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1171,21 +1171,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>3298</v>
+        <v>6464</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1195,10 +1195,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>453014</v>
+        <v>453095</v>
       </c>
       <c r="R7" t="n">
-        <v>6911798</v>
+        <v>6911956</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1260,7 +1260,7 @@
         <v>129910381</v>
       </c>
       <c r="B8" t="n">
-        <v>80285</v>
+        <v>80200</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1357,7 +1357,7 @@
         <v>129910380</v>
       </c>
       <c r="B9" t="n">
-        <v>79180</v>
+        <v>79095</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1454,7 +1454,7 @@
         <v>129910392</v>
       </c>
       <c r="B10" t="n">
-        <v>91748</v>
+        <v>91661</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1547,7 +1547,7 @@
         <v>129910391</v>
       </c>
       <c r="B11" t="n">
-        <v>96146</v>
+        <v>96059</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1644,7 +1644,7 @@
         <v>129910393</v>
       </c>
       <c r="B12" t="n">
-        <v>91728</v>
+        <v>91641</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1741,7 +1741,7 @@
         <v>129910397</v>
       </c>
       <c r="B13" t="n">
-        <v>91692</v>
+        <v>91605</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1838,7 +1838,7 @@
         <v>129910388</v>
       </c>
       <c r="B14" t="n">
-        <v>79180</v>
+        <v>79095</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1935,7 +1935,7 @@
         <v>129910390</v>
       </c>
       <c r="B15" t="n">
-        <v>91692</v>
+        <v>91605</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2032,7 +2032,7 @@
         <v>129910398</v>
       </c>
       <c r="B16" t="n">
-        <v>91728</v>
+        <v>91641</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
